--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3830" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3831" uniqueCount="572">
   <si>
     <t>Property</t>
   </si>
@@ -1411,7 +1411,10 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -11154,9 +11157,11 @@
       <c r="X75" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="Y75" s="2"/>
+      <c r="Y75" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="Z75" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11192,27 +11197,27 @@
         <v>83</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11238,16 +11243,16 @@
         <v>198</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
@@ -11275,10 +11280,10 @@
         <v>332</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -11296,7 +11301,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11317,10 +11322,10 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11331,10 +11336,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11357,16 +11362,16 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11416,7 +11421,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11434,27 +11439,27 @@
         <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11477,16 +11482,16 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11536,7 +11541,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11554,27 +11559,27 @@
         <v>83</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11597,19 +11602,19 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -11658,7 +11663,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11670,7 +11675,7 @@
         <v>83</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>83</v>
@@ -11679,10 +11684,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11693,10 +11698,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11811,10 +11816,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11931,14 +11936,14 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11960,10 +11965,10 @@
         <v>139</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>156</v>
@@ -12018,7 +12023,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12053,10 +12058,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12079,13 +12084,13 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12136,7 +12141,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12145,7 +12150,7 @@
         <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>106</v>
@@ -12157,10 +12162,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12171,10 +12176,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12197,13 +12202,13 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12254,7 +12259,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12263,7 +12268,7 @@
         <v>94</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>106</v>
@@ -12275,10 +12280,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12289,10 +12294,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12318,16 +12323,16 @@
         <v>198</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12355,10 +12360,10 @@
         <v>118</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
@@ -12376,7 +12381,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12394,10 +12399,10 @@
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>433</v>
@@ -12411,10 +12416,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12440,16 +12445,16 @@
         <v>198</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12477,10 +12482,10 @@
         <v>332</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>83</v>
@@ -12498,7 +12503,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12516,10 +12521,10 @@
         <v>83</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>433</v>
@@ -12533,10 +12538,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12559,17 +12564,17 @@
         <v>83</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -12618,7 +12623,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12642,7 +12647,7 @@
         <v>83</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12653,10 +12658,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12682,10 +12687,10 @@
         <v>214</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12736,7 +12741,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12757,10 +12762,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12771,10 +12776,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12797,16 +12802,16 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12856,7 +12861,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12877,10 +12882,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12891,10 +12896,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12917,16 +12922,16 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12976,7 +12981,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -12997,10 +13002,10 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13011,10 +13016,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13037,19 +13042,19 @@
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13098,7 +13103,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13119,10 +13124,10 @@
         <v>83</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13133,10 +13138,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13251,10 +13256,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13371,14 +13376,14 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13400,10 +13405,10 @@
         <v>139</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>156</v>
@@ -13458,7 +13463,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13493,10 +13498,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13522,13 +13527,13 @@
         <v>198</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O95" t="s" s="2">
         <v>331</v>
@@ -13580,7 +13585,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>94</v>
@@ -13598,7 +13603,7 @@
         <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>337</v>
@@ -13615,10 +13620,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13641,16 +13646,16 @@
         <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O96" t="s" s="2">
         <v>408</v>
@@ -13702,7 +13707,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13720,7 +13725,7 @@
         <v>83</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>412</v>
@@ -13737,10 +13742,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13766,13 +13771,13 @@
         <v>198</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O97" t="s" s="2">
         <v>418</v>
@@ -13824,7 +13829,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13859,10 +13864,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13888,16 +13893,16 @@
         <v>198</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -13946,7 +13951,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -13981,10 +13986,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14010,16 +14015,16 @@
         <v>84</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14068,7 +14073,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14089,10 +14094,10 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
